--- a/data/trans_dic/P21B_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P21B_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,84</t>
+          <t>0,0; 12,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,53</t>
+          <t>0,95; 8,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 14,0</t>
+          <t>1,97; 14,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 14,93</t>
+          <t>2,3; 11,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,2</t>
+          <t>0,0; 12,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,65</t>
+          <t>0,89; 10,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 9,53</t>
+          <t>2,75; 9,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,87</t>
+          <t>0,99; 8,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,11</t>
+          <t>0,46; 4,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 8,8</t>
+          <t>2,03; 9,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 10,06</t>
+          <t>3,25; 8,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,83</t>
+          <t>0,0; 12,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,89</t>
+          <t>0,7; 5,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 14,35</t>
+          <t>1,27; 14,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 14,72</t>
+          <t>1,64; 14,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,79</t>
+          <t>0,99; 7,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 10,16</t>
+          <t>1,79; 9,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 8,61</t>
+          <t>1,75; 8,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,98</t>
+          <t>0,86; 6,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,24</t>
+          <t>1,19; 5,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,72</t>
+          <t>2,59; 9,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,83</t>
+          <t>2,61; 9,57</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,69</t>
+          <t>1,29; 12,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,93</t>
+          <t>0,0; 6,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 18,97</t>
+          <t>2,4; 18,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,28; 16,7</t>
+          <t>3,12; 13,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,97</t>
+          <t>0,0; 10,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 20,49</t>
+          <t>3,91; 21,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,2</t>
+          <t>1,01; 8,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,26</t>
+          <t>0,57; 4,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,26</t>
+          <t>0,58; 6,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 16,2</t>
+          <t>4,21; 15,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,86</t>
+          <t>2,48; 8,04</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,76</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,83</t>
+          <t>0,0; 14,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 11,37</t>
+          <t>0,96; 10,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 25,15</t>
+          <t>1,35; 22,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,05</t>
+          <t>0,82; 6,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,34</t>
+          <t>0,95; 8,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 16,18</t>
+          <t>3,99; 16,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 14,49</t>
+          <t>3,52; 13,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,63</t>
+          <t>0,97; 5,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 7,71</t>
+          <t>1,61; 8,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 11,02</t>
+          <t>3,63; 10,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 15,34</t>
+          <t>3,58; 14,46</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,53</t>
+          <t>0,0; 16,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,17 +1292,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,26</t>
+          <t>0,0; 26,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,18</t>
+          <t>0,0; 15,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,44</t>
+          <t>0,0; 8,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,78</t>
+          <t>0,0; 10,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,42</t>
+          <t>0,88; 8,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,83</t>
+          <t>0,0; 16,45</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1432,17 +1432,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,81</t>
+          <t>0,64; 8,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 6,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,46</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,25</t>
+          <t>0,65; 7,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 5,51</t>
+          <t>1,21; 5,91</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 16,81</t>
+          <t>4,59; 15,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 16,01</t>
+          <t>3,02; 16,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,12; 19,66</t>
+          <t>8,73; 19,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,41</t>
+          <t>3,41; 11,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,52</t>
+          <t>1,62; 7,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,65; 18,34</t>
+          <t>5,23; 16,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 15,85</t>
+          <t>10,35; 18,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 11,33</t>
+          <t>4,6; 11,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,92</t>
+          <t>1,23; 4,99</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,57; 14,54</t>
+          <t>5,77; 14,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 14,94</t>
+          <t>10,81; 17,35</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 11,03</t>
+          <t>1,1; 10,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,6</t>
+          <t>0,0; 9,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,12; 23,18</t>
+          <t>9,16; 24,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,21; 11,7</t>
+          <t>2,27; 11,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,27</t>
+          <t>0,67; 6,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,02; 14,88</t>
+          <t>3,6; 15,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,58; 18,25</t>
+          <t>6,92; 18,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,73; 15,91</t>
+          <t>5,12; 16,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,19</t>
+          <t>1,47; 6,49</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,46</t>
+          <t>2,85; 10,79</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,94; 18,0</t>
+          <t>8,59; 18,05</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,9; 12,27</t>
+          <t>4,84; 11,86</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,27</t>
+          <t>2,59; 6,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,76</t>
+          <t>1,29; 3,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,34</t>
+          <t>4,74; 8,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,89; 10,51</t>
+          <t>5,95; 10,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,31</t>
+          <t>1,93; 4,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,42</t>
+          <t>2,09; 4,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,42</t>
+          <t>5,27; 9,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,64</t>
+          <t>6,4; 9,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,5</t>
+          <t>2,49; 4,5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,76</t>
+          <t>2,08; 3,74</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,39</t>
+          <t>5,46; 8,44</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,4</t>
+          <t>6,6; 9,34</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>5966</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>12168</t>
         </is>
       </c>
     </row>
@@ -2209,27 +2209,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4953</t>
+          <t>0; 4906</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>954; 8616</t>
+          <t>959; 8388</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1080; 11714</t>
+          <t>1648; 11994</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2838; 15970</t>
+          <t>2444; 12530</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7406</t>
+          <t>0; 7236</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2239,32 +2239,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>917; 10049</t>
+          <t>931; 10541</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2788; 10811</t>
+          <t>3347; 11234</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>924; 8393</t>
+          <t>934; 8405</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>975; 8714</t>
+          <t>973; 8926</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3333; 16519</t>
+          <t>3810; 17765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7796; 22185</t>
+          <t>7407; 19673</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>9396</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8927</t>
+          <t>0; 9114</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>929; 7732</t>
+          <t>924; 7548</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1049; 11853</t>
+          <t>1049; 12089</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1178; 11573</t>
+          <t>1328; 11921</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5872</t>
+          <t>0; 6136</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1981; 13524</t>
+          <t>1980; 15557</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1936; 11061</t>
+          <t>1945; 10820</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1683; 8873</t>
+          <t>1895; 9645</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1041; 12168</t>
+          <t>1759; 13558</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3885; 17319</t>
+          <t>3927; 17475</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4176; 18608</t>
+          <t>4963; 17992</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4290; 16051</t>
+          <t>4942; 18102</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>9137</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>863; 7316</t>
+          <t>883; 8424</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6066</t>
+          <t>0; 5230</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>857; 6736</t>
+          <t>854; 6559</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2359; 11992</t>
+          <t>2333; 10134</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,37 +2650,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 9599</t>
+          <t>0; 10057</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1642; 9272</t>
+          <t>1767; 9843</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1143; 10324</t>
+          <t>1155; 9284</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>879; 8116</t>
+          <t>884; 7166</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>986; 10821</t>
+          <t>995; 10737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3427; 13084</t>
+          <t>3397; 12774</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4522; 16306</t>
+          <t>4699; 15232</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>14440</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6539</t>
+          <t>0; 6250</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 10334</t>
+          <t>0; 11415</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>944; 10952</t>
+          <t>923; 10550</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1212; 19197</t>
+          <t>1221; 20011</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>847; 7312</t>
+          <t>847; 7230</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1026; 9772</t>
+          <t>990; 9027</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5526; 20096</t>
+          <t>4960; 20202</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3593; 13351</t>
+          <t>3761; 14714</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1762; 10051</t>
+          <t>1727; 9916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2684; 14283</t>
+          <t>2988; 16101</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7958; 24310</t>
+          <t>8001; 24192</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6810; 25848</t>
+          <t>7055; 28457</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1495</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7201</t>
+          <t>0; 6210</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,17 +3056,17 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4519</t>
+          <t>0; 5039</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6381</t>
+          <t>0; 6449</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6659</t>
+          <t>0; 6654</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 8284</t>
+          <t>0; 8042</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>982; 9753</t>
+          <t>1017; 9675</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 4321</t>
+          <t>0; 4901</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>4000</t>
         </is>
       </c>
     </row>
@@ -3264,17 +3264,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>451; 5374</t>
+          <t>434; 5918</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6001</t>
+          <t>0; 5637</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5252</t>
+          <t>0; 4822</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,17 +3284,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>528; 5493</t>
+          <t>500; 5966</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5904</t>
+          <t>0; 5458</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4863</t>
+          <t>0; 4825</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1588; 7972</t>
+          <t>1756; 8605</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22164</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>32022</t>
+          <t>37030</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>54186</t>
+          <t>62831</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4481; 18360</t>
+          <t>5013; 17361</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5554</t>
+          <t>0; 6324</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2174; 11892</t>
+          <t>2241; 12285</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15271; 32924</t>
+          <t>16765; 37160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5411; 19249</t>
+          <t>5749; 18676</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2942; 13967</t>
+          <t>3011; 14148</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6912; 22417</t>
+          <t>6395; 20631</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>7459; 67906</t>
+          <t>27561; 48206</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12976; 31496</t>
+          <t>12772; 31310</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4651; 16248</t>
+          <t>4055; 16493</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10946; 28573</t>
+          <t>11345; 28519</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>20307; 89043</t>
+          <t>49544; 79516</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16070</t>
+          <t>18019</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1088; 10899</t>
+          <t>1091; 10729</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6564</t>
+          <t>0; 6363</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8040; 22941</t>
+          <t>9066; 24587</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1968; 10419</t>
+          <t>2299; 12073</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1144; 9532</t>
+          <t>1015; 9146</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3190; 15722</t>
+          <t>3803; 16174</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9251; 25662</t>
+          <t>9724; 26489</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6375; 17703</t>
+          <t>6599; 20752</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3625; 15529</t>
+          <t>3684; 16274</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4890; 18207</t>
+          <t>4962; 18782</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21419; 43134</t>
+          <t>20592; 43257</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9817; 24578</t>
+          <t>11143; 27327</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53665</t>
+          <t>57833</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>66627</t>
+          <t>73654</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>120292</t>
+          <t>131486</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>15263; 35006</t>
+          <t>14448; 35954</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9291; 26442</t>
+          <t>9048; 25751</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26552; 51514</t>
+          <t>26160; 49407</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39799; 71077</t>
+          <t>43599; 79154</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>15672; 35543</t>
+          <t>15880; 35103</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20624; 43213</t>
+          <t>20445; 44572</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39491; 70597</t>
+          <t>39470; 71959</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>35499; 90445</t>
+          <t>59838; 90891</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>33647; 62143</t>
+          <t>34462; 62244</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34503; 63203</t>
+          <t>35008; 62867</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>71145; 109142</t>
+          <t>70960; 109790</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>79066; 144678</t>
+          <t>110035; 155707</t>
         </is>
       </c>
     </row>
